--- a/Data/AttackInfo.xlsx
+++ b/Data/AttackInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992369FC-D02F-42CF-BFE4-DC39126091E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1580F49-613D-4661-BF3B-03756AEADAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3990" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>damage</t>
   </si>
   <si>
     <t>knockBack</t>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -358,26 +370,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>10</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
